--- a/docs/Labels.xlsx
+++ b/docs/Labels.xlsx
@@ -89,17 +89,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AboutSettings_AccentNote_Text</t>
+          <t xml:space="preserve">AboutSettings_Architecture_Label</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The accent colour comes from the active theme.</t>
+          <t xml:space="preserve">Architecture</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El color de acento proviene del tema activo.</t>
+          <t xml:space="preserve">Arquitectura</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -121,17 +121,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AboutSettings_Architecture_Label</t>
+          <t xml:space="preserve">AboutSettings_Build_Label</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Architecture</t>
+          <t xml:space="preserve">Build</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arquitectura</t>
+          <t xml:space="preserve">Compilación</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -153,17 +153,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AboutSettings_Build_Label</t>
+          <t xml:space="preserve">AboutSettings_Description_Text</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Build</t>
+          <t xml:space="preserve">Tracker monitors the prices of your Amazon products across marketplaces, charts their history and highlights the best deals.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compilación</t>
+          <t xml:space="preserve">Tracker monitoriza los precios de tus productos de Amazon en varios marketplaces, dibuja su histórico y destaca las mejores ofertas.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -185,17 +185,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AboutSettings_Copyright_Text</t>
+          <t xml:space="preserve">AboutSettings_Details_Header</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Built with WinUI 3 and the Windows App SDK.</t>
+          <t xml:space="preserve">DETAILS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hecho con WinUI 3 y el Windows App SDK.</t>
+          <t xml:space="preserve">DETALLES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -217,17 +217,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AboutSettings_Description_Text</t>
+          <t xml:space="preserve">AboutSettings_DevelopedBy_Label</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracker monitors the prices of your Amazon products across marketplaces, charts their history and highlights the best deals.</t>
+          <t xml:space="preserve">Developed by</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracker monitoriza los precios de tus productos de Amazon en varios marketplaces, dibuja su histórico y destaca las mejores ofertas.</t>
+          <t xml:space="preserve">Desarrollado por</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -249,17 +249,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">AboutSettings_Details_Header</t>
+          <t xml:space="preserve">AboutSettings_Runtime_Label</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Details</t>
+          <t xml:space="preserve">Runtime</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detalles</t>
+          <t xml:space="preserve">Runtime</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -281,17 +281,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">AboutSettings_Runtime_Label</t>
+          <t xml:space="preserve">AboutSettings_ThirdParty_Header</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Runtime</t>
+          <t xml:space="preserve">THIRD-PARTY COMPONENTS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Runtime</t>
+          <t xml:space="preserve">COMPONENTES DE TERCEROS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -308,22 +308,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes → About</t>
+          <t xml:space="preserve">Ajustes → General</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">AboutSettings_Tagline_Text</t>
+          <t xml:space="preserve">GeneralSettings_AutoRefreshHours_Label</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amazon price tracker</t>
+          <t xml:space="preserve">Refresh prices (hours)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rastreador de precios de Amazon</t>
+          <t xml:space="preserve">Actualizar precios (horas)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -340,22 +340,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes → About</t>
+          <t xml:space="preserve">Ajustes → General</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">AboutSettings_ThirdParty_Header</t>
+          <t xml:space="preserve">GeneralSettings_DataSection_Header</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Third-party components</t>
+          <t xml:space="preserve">DATA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Componentes de terceros</t>
+          <t xml:space="preserve">DATOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -377,17 +377,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GeneralSettings_AutoRefreshHours_Label</t>
+          <t xml:space="preserve">GeneralSettings_DollarsPerEuro_Label</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auto-refresh prices every (hours)</t>
+          <t xml:space="preserve">Dollars per euro (amazon.com)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Actualizar precios cada (horas)</t>
+          <t xml:space="preserve">Dólares por euro (amazon.com)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -441,17 +441,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GeneralSettings_Language_Label</t>
+          <t xml:space="preserve">GeneralSettings_InterfaceSection_Header</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Language</t>
+          <t xml:space="preserve">INTERFACE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idioma</t>
+          <t xml:space="preserve">INTERFAZ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GeneralSettings_LogExceptions_Label</t>
+          <t xml:space="preserve">GeneralSettings_Language_Label</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Log exceptions to a file</t>
+          <t xml:space="preserve">Language</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registrar excepciones en un fichero</t>
+          <t xml:space="preserve">Idioma</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -505,17 +505,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GeneralSettings_ShowWidgetHeader_Label</t>
+          <t xml:space="preserve">GeneralSettings_LogExceptions_Label</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Show widget headers</t>
+          <t xml:space="preserve">Log exceptions</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mostrar la cabecera de los widgets</t>
+          <t xml:space="preserve">Registrar excepciones</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -532,22 +532,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes → Theme</t>
+          <t xml:space="preserve">Ajustes → General</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeSettings_BackgroundOverlay_Header</t>
+          <t xml:space="preserve">GeneralSettings_MinimizeToTray_Label</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Background Overlay</t>
+          <t xml:space="preserve">Close to system tray</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overlay del fondo</t>
+          <t xml:space="preserve">Cerrar a la bandeja del sistema</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -564,22 +564,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes → Theme</t>
+          <t xml:space="preserve">Ajustes → General</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeSettings_EditColors_Label</t>
+          <t xml:space="preserve">GeneralSettings_RestoreMaximized_Label</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Custom colours...</t>
+          <t xml:space="preserve">Restore maximised</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colores personalizados...</t>
+          <t xml:space="preserve">Restaurar maximizada</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -596,22 +596,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes → Theme</t>
+          <t xml:space="preserve">Ajustes → General</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeSettings_OverlayBlur_Label</t>
+          <t xml:space="preserve">GeneralSettings_ShowWidgetHeader_Label</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overlay blur</t>
+          <t xml:space="preserve">Show widget headers</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desenfoque del overlay</t>
+          <t xml:space="preserve">Mostrar la cabecera de los widgets</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -628,22 +628,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes → Theme</t>
+          <t xml:space="preserve">Ajustes → General</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeSettings_OverlayOpacity_Label</t>
+          <t xml:space="preserve">GeneralSettings_StartMinimized_Label</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overlay opacity</t>
+          <t xml:space="preserve">Start minimised (system tray)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opacidad del overlay</t>
+          <t xml:space="preserve">Iniciar minimizada (bandeja del sistema)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -660,22 +660,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes → Theme</t>
+          <t xml:space="preserve">Ajustes → General</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeSettings_RandomTheme_Label</t>
+          <t xml:space="preserve">GeneralSettings_StartWithWindows_Label</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pick a random theme on each launch</t>
+          <t xml:space="preserve">Start with Windows</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elegir un tema al azar en cada arranque</t>
+          <t xml:space="preserve">Iniciar con Windows</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -692,22 +692,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes → Theme</t>
+          <t xml:space="preserve">Ajustes → General</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeSettings_Theme_Label</t>
+          <t xml:space="preserve">GeneralSettings_WindowSection_Header</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theme</t>
+          <t xml:space="preserve">WINDOW</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tema</t>
+          <t xml:space="preserve">VENTANA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -724,22 +724,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes → Theme</t>
+          <t xml:space="preserve">Ajustes → General</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeSettings_TintBrightness_Label</t>
+          <t xml:space="preserve">GeneralSettings_YensPerEuro_Label</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tint brightness</t>
+          <t xml:space="preserve">Yen per euro (amazon.co.jp)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brillo del tinte</t>
+          <t xml:space="preserve">Yenes por euro (amazon.co.jp)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeSettings_TintOpacity_Label</t>
+          <t xml:space="preserve">ThemeSettings_BackgroundOverlay_Header</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tint opacity</t>
+          <t xml:space="preserve">BACKGROUND OVERLAY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opacidad del tinte</t>
+          <t xml:space="preserve">OVERLAY DEL FONDO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeSettings_TintSaturation_Label</t>
+          <t xml:space="preserve">ThemeSettings_EditColors_Label</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tint saturation</t>
+          <t xml:space="preserve">Custom colours...</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saturación del tinte</t>
+          <t xml:space="preserve">Colores personalizados...</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -825,17 +825,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeSettings_UseCustomColors_Label</t>
+          <t xml:space="preserve">ThemeSettings_OverlayBlur_Label</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Use custom colours</t>
+          <t xml:space="preserve">Overlay blur</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Usar colores personalizados</t>
+          <t xml:space="preserve">Desenfoque del overlay</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -852,22 +852,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes rápidos (toolbar)</t>
+          <t xml:space="preserve">Ajustes → Theme</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">QuickSettings_CornerRadius_Label</t>
+          <t xml:space="preserve">ThemeSettings_OverlayOpacity_Label</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corner radius</t>
+          <t xml:space="preserve">Overlay opacity</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Redondeo de bordes</t>
+          <t xml:space="preserve">Opacidad del overlay</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -884,22 +884,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes rápidos (toolbar)</t>
+          <t xml:space="preserve">Ajustes → Theme</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">QuickSettings_Gap_Label</t>
+          <t xml:space="preserve">ThemeSettings_RandomTheme_Label</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gap</t>
+          <t xml:space="preserve">Random theme on launch</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Separación</t>
+          <t xml:space="preserve">Tema al azar al arrancar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -916,22 +916,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes rápidos (toolbar)</t>
+          <t xml:space="preserve">Ajustes → Theme</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">QuickSettings_PanelMargin_Label</t>
+          <t xml:space="preserve">ThemeSettings_Theme_Label</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panel margin</t>
+          <t xml:space="preserve">Theme</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margen del panel</t>
+          <t xml:space="preserve">Tema</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -948,22 +948,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajustes rápidos (toolbar)</t>
+          <t xml:space="preserve">Ajustes → Theme</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">QuickSettings_Widgets_Header</t>
+          <t xml:space="preserve">ThemeSettings_ThemeSection_Header</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WIDGETS</t>
+          <t xml:space="preserve">THEME</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WIDGETS</t>
+          <t xml:space="preserve">TEMA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -980,22 +980,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Añadir producto (diálogo)</t>
+          <t xml:space="preserve">Ajustes → Theme</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">AddProduct_Dialog_Message</t>
+          <t xml:space="preserve">ThemeSettings_TintBrightness_Label</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paste the product URL</t>
+          <t xml:space="preserve">Tint brightness</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pega la URL del producto</t>
+          <t xml:space="preserve">Brillo del tinte</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1012,22 +1012,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Añadir producto (diálogo)</t>
+          <t xml:space="preserve">Ajustes → Theme</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AddProduct_Dialog_Title</t>
+          <t xml:space="preserve">ThemeSettings_TintOpacity_Label</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Track a product</t>
+          <t xml:space="preserve">Tint opacity</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rastrear un producto</t>
+          <t xml:space="preserve">Opacidad del tinte</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1044,22 +1044,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Añadir producto (diálogo)</t>
+          <t xml:space="preserve">Ajustes → Theme</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">AddProduct_Duplicate_Message</t>
+          <t xml:space="preserve">ThemeSettings_TintSaturation_Label</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">This product is already being tracked, so it will not be added again.</t>
+          <t xml:space="preserve">Tint saturation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Este producto ya se está rastreando, así que no se añadirá de nuevo.</t>
+          <t xml:space="preserve">Saturación del tinte</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1076,22 +1076,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Añadir producto (diálogo)</t>
+          <t xml:space="preserve">Ajustes → Theme</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AddProduct_Duplicate_Title</t>
+          <t xml:space="preserve">ThemeSettings_UseCustomColors_Label</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product already tracked</t>
+          <t xml:space="preserve">Use custom colours</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Producto ya rastreado</t>
+          <t xml:space="preserve">Usar colores personalizados</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1108,22 +1108,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Añadir producto (diálogo)</t>
+          <t xml:space="preserve">Ajustes rápidos (toolbar)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">AddProduct_Url_Placeholder</t>
+          <t xml:space="preserve">QuickSettings_CornerRadius_Label</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.amazon.es/...</t>
+          <t xml:space="preserve">Widget Corner</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.amazon.es/...</t>
+          <t xml:space="preserve">Borde de widgets</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1140,22 +1140,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra de herramientas superior</t>
+          <t xml:space="preserve">Ajustes rápidos (toolbar)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toolbar_SaveTemplate_Tooltip</t>
+          <t xml:space="preserve">QuickSettings_Gap_Label</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Save layout as template</t>
+          <t xml:space="preserve">Widget Gap</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guardar la disposición como plantilla</t>
+          <t xml:space="preserve">Separación entre widgets</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1172,22 +1172,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra de herramientas superior</t>
+          <t xml:space="preserve">Ajustes rápidos (toolbar)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toolbar_Settings_Tooltip</t>
+          <t xml:space="preserve">QuickSettings_PanelMargin_Label</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settings</t>
+          <t xml:space="preserve">Widget Panel Margin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuración</t>
+          <t xml:space="preserve">Margen del panel</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1204,22 +1204,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra de herramientas superior</t>
+          <t xml:space="preserve">Añadir producto (diálogo)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toolbar_Templates_Tooltip</t>
+          <t xml:space="preserve">AddProduct_Dialog_Message</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates</t>
+          <t xml:space="preserve">Product URL:</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantillas</t>
+          <t xml:space="preserve">URL del producto:</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1236,22 +1236,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra de progreso / operaciones</t>
+          <t xml:space="preserve">Añadir producto (diálogo)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress_LazyLoaded_Progress</t>
+          <t xml:space="preserve">AddProduct_Dialog_Title</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}{1} media files loaded</t>
+          <t xml:space="preserve">Track a product</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}{1} archivos multimedia cargados</t>
+          <t xml:space="preserve">Rastrear un producto</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra de progreso / operaciones</t>
+          <t xml:space="preserve">Añadir producto (diálogo)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progress_LazyLoading_Progress</t>
+          <t xml:space="preserve">AddProduct_Duplicate_Message</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}Loading {1} media files</t>
+          <t xml:space="preserve">This product is already being tracked, so it will not be added again.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}Cargando {1} archivos multimedia</t>
+          <t xml:space="preserve">Este producto ya se está rastreando, así que no se añadirá de nuevo.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1300,22 +1300,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra inferior (footer)</t>
+          <t xml:space="preserve">Añadir producto (diálogo)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer_AddProduct_Tooltip</t>
+          <t xml:space="preserve">AddProduct_Duplicate_Title</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add product</t>
+          <t xml:space="preserve">Product already tracked</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Añadir producto</t>
+          <t xml:space="preserve">Producto ya rastreado</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1332,22 +1332,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra inferior (footer)</t>
+          <t xml:space="preserve">Añadir producto (diálogo)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer_AxisLabels_Tooltip</t>
+          <t xml:space="preserve">AddProduct_Url_Placeholder</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toggle chart axis labels visibility</t>
+          <t xml:space="preserve">https://www.amazon.es/...</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mostrar u ocultar las etiquetas de los ejes</t>
+          <t xml:space="preserve">https://www.amazon.es/...</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1364,22 +1364,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra inferior (footer)</t>
+          <t xml:space="preserve">Bandeja del sistema</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer_IncludeShipping_Tooltip</t>
+          <t xml:space="preserve">Tray_Exit_Label</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Include shipping cost in the price</t>
+          <t xml:space="preserve">Exit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incluir los gastos de envío en el precio</t>
+          <t xml:space="preserve">Salir</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1396,22 +1396,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra inferior (footer)</t>
+          <t xml:space="preserve">Bandeja del sistema</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer_MinChart_Tooltip</t>
+          <t xml:space="preserve">Tray_Hide_Label</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toggle lowest price evolution chart</t>
+          <t xml:space="preserve">Hide</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mostrar u ocultar la gráfica de evolución del precio mínimo</t>
+          <t xml:space="preserve">Ocultar</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1428,22 +1428,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra inferior (footer)</t>
+          <t xml:space="preserve">Bandeja del sistema</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer_NextUpdate_Tooltip</t>
+          <t xml:space="preserve">Tray_Show_Label</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Next automatic price update</t>
+          <t xml:space="preserve">Show</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siguiente actualización automática de precios</t>
+          <t xml:space="preserve">Mostrar</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1460,22 +1460,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra inferior (footer)</t>
+          <t xml:space="preserve">Barra de herramientas superior</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer_RefreshAll_LastUpdate_Format</t>
+          <t xml:space="preserve">Toolbar_Settings_Tooltip</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last refresh: {0}</t>
+          <t xml:space="preserve">Settings</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Último refresco: {0}</t>
+          <t xml:space="preserve">Configuración</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1492,22 +1492,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra inferior (footer)</t>
+          <t xml:space="preserve">Barra de herramientas superior</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer_RefreshAll_LastUpdate_Never</t>
+          <t xml:space="preserve">Toolbar_Templates_Tooltip</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last refresh: never</t>
+          <t xml:space="preserve">Templates</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Último refresco: nunca</t>
+          <t xml:space="preserve">Plantillas</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1524,22 +1524,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra inferior (footer)</t>
+          <t xml:space="preserve">Barra de progreso / operaciones</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer_RefreshAll_Tooltip</t>
+          <t xml:space="preserve">Progress_LazyLoaded_Progress</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refresh all prices</t>
+          <t xml:space="preserve">{0}{1} media files loaded</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refrescar todos los precios</t>
+          <t xml:space="preserve">{0}{1} archivos multimedia cargados</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1556,22 +1556,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra inferior (footer)</t>
+          <t xml:space="preserve">Barra de progreso / operaciones</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer_ShowPurchased_Tooltip</t>
+          <t xml:space="preserve">Progress_LazyLoading_Progress</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Show/hide purchased products</t>
+          <t xml:space="preserve">{0}Loading {1} media files</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mostrar/ocultar productos comprados</t>
+          <t xml:space="preserve">{0}Cargando {1} archivos multimedia</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1593,17 +1593,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Footer_Tooltips_Tooltip</t>
+          <t xml:space="preserve">Footer_AddProduct_Tooltip</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Show/hide button tooltips</t>
+          <t xml:space="preserve">Add product</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mostrar/ocultar los tooltips de los botones</t>
+          <t xml:space="preserve">Añadir producto</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1620,22 +1620,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Común (botones de diálogo)</t>
+          <t xml:space="preserve">Barra inferior (footer)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common_Add_Label</t>
+          <t xml:space="preserve">Footer_AxisLabels_Tooltip</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add</t>
+          <t xml:space="preserve">Toggle chart axis labels</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Añadir</t>
+          <t xml:space="preserve">Alternar las etiquetas de los ejes</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1652,22 +1652,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Común (botones de diálogo)</t>
+          <t xml:space="preserve">Barra inferior (footer)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common_Apply_Label</t>
+          <t xml:space="preserve">Footer_IncludeShipping_Tooltip</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apply</t>
+          <t xml:space="preserve">Include shipping cost</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aplicar</t>
+          <t xml:space="preserve">Incluir gastos de envío</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1684,22 +1684,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Común (botones de diálogo)</t>
+          <t xml:space="preserve">Barra inferior (footer)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common_AppName</t>
+          <t xml:space="preserve">Footer_MinChart_Tooltip</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracker</t>
+          <t xml:space="preserve">Toggle lowest price chart</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracker</t>
+          <t xml:space="preserve">Alternar la gráfica de precio mínimo</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1716,22 +1716,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Común (botones de diálogo)</t>
+          <t xml:space="preserve">Barra inferior (footer)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common_Cancel_Label</t>
+          <t xml:space="preserve">Footer_NextUpdate_Tooltip</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cancel</t>
+          <t xml:space="preserve">Next automatic price update</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cancelar</t>
+          <t xml:space="preserve">Siguiente actualización automática de precios</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1748,22 +1748,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Común (botones de diálogo)</t>
+          <t xml:space="preserve">Barra inferior (footer)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common_Delete_Label</t>
+          <t xml:space="preserve">Footer_RefreshAll_LastUpdate_Format</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete</t>
+          <t xml:space="preserve">Last refresh: {0}</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borrar</t>
+          <t xml:space="preserve">Último refresco: {0}</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1780,22 +1780,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Común (botones de diálogo)</t>
+          <t xml:space="preserve">Barra inferior (footer)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common_OK_Label</t>
+          <t xml:space="preserve">Footer_RefreshAll_LastUpdate_Never</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">OK</t>
+          <t xml:space="preserve">Last refresh: never</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aceptar</t>
+          <t xml:space="preserve">Último refresco: nunca</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1812,22 +1812,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Común (botones de diálogo)</t>
+          <t xml:space="preserve">Barra inferior (footer)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common_Save_Label</t>
+          <t xml:space="preserve">Footer_RefreshAll_Tooltip</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Save</t>
+          <t xml:space="preserve">Refresh all prices</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guardar</t>
+          <t xml:space="preserve">Refrescar todos los precios</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1844,22 +1844,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diálogo guardar plantilla</t>
+          <t xml:space="preserve">Barra inferior (footer)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">TemplateNameDialog_ChooseSlot_Text</t>
+          <t xml:space="preserve">Footer_ShowPurchased_Tooltip</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Choose a slot to save into (an occupied slot will be overwritten):</t>
+          <t xml:space="preserve">Show/hide purchased products</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elige un slot donde guardar (si está ocupado se sobrescribe):</t>
+          <t xml:space="preserve">Mostrar/ocultar productos comprados</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1876,22 +1876,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diálogo guardar plantilla</t>
+          <t xml:space="preserve">Barra inferior (footer)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TemplateNameDialog_Name_Label</t>
+          <t xml:space="preserve">Footer_Tooltips_Tooltip</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Toggle tooltips</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre</t>
+          <t xml:space="preserve">Alternar los tooltips</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1908,22 +1908,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diálogo guardar plantilla</t>
+          <t xml:space="preserve">Común (botones de diálogo)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TemplateNameDialog_Name_Placeholder</t>
+          <t xml:space="preserve">Common_Add_Label</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Template name</t>
+          <t xml:space="preserve">Add</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre de la plantilla</t>
+          <t xml:space="preserve">Añadir</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1940,22 +1940,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diálogos (títulos)</t>
+          <t xml:space="preserve">Común (botones de diálogo)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">DialogsService_SaveTemplate_Title</t>
+          <t xml:space="preserve">Common_Apply_Label</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Save template</t>
+          <t xml:space="preserve">Apply</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guardar plantilla</t>
+          <t xml:space="preserve">Aplicar</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1972,22 +1972,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diálogos (títulos)</t>
+          <t xml:space="preserve">Común (botones de diálogo)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">DialogsService_Settings_Title</t>
+          <t xml:space="preserve">Common_AppName</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settings</t>
+          <t xml:space="preserve">TRACKER</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuración</t>
+          <t xml:space="preserve">TRACKER</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2004,22 +2004,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editor de colores del tema</t>
+          <t xml:space="preserve">Común (botones de diálogo)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_Accent</t>
+          <t xml:space="preserve">Common_Cancel_Label</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accent</t>
+          <t xml:space="preserve">Cancel</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acento</t>
+          <t xml:space="preserve">Cancelar</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2036,22 +2036,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editor de colores del tema</t>
+          <t xml:space="preserve">Común (botones de diálogo)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_AccentDark</t>
+          <t xml:space="preserve">Common_Delete_Label</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accent dark</t>
+          <t xml:space="preserve">Delete</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acento oscuro</t>
+          <t xml:space="preserve">Borrar</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2068,22 +2068,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editor de colores del tema</t>
+          <t xml:space="preserve">Común (botones de diálogo)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_AccentLight</t>
+          <t xml:space="preserve">Common_OK_Label</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accent light</t>
+          <t xml:space="preserve">OK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acento claro</t>
+          <t xml:space="preserve">Aceptar</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2100,22 +2100,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editor de colores del tema</t>
+          <t xml:space="preserve">Común (botones de diálogo)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_Background</t>
+          <t xml:space="preserve">Common_Save_Label</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Background</t>
+          <t xml:space="preserve">Save</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondo</t>
+          <t xml:space="preserve">Guardar</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2132,22 +2132,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editor de colores del tema</t>
+          <t xml:space="preserve">Diálogos (títulos)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_BackgroundLight</t>
+          <t xml:space="preserve">DialogsService_Settings_Title</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Background light</t>
+          <t xml:space="preserve">Settings</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondo claro</t>
+          <t xml:space="preserve">Configuración</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2169,17 +2169,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_CardBackground</t>
+          <t xml:space="preserve">ThemeColors_Name_Accent</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card</t>
+          <t xml:space="preserve">Accent</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarjeta</t>
+          <t xml:space="preserve">Acento</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_CardBackgroundLight</t>
+          <t xml:space="preserve">ThemeColors_Name_AccentDark</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Card light</t>
+          <t xml:space="preserve">Accent dark</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarjeta clara</t>
+          <t xml:space="preserve">Acento oscuro</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_Danger</t>
+          <t xml:space="preserve">ThemeColors_Name_AccentLight</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danger</t>
+          <t xml:space="preserve">Accent light</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peligro</t>
+          <t xml:space="preserve">Acento claro</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2265,17 +2265,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_ExtraColor1</t>
+          <t xml:space="preserve">ThemeColors_Name_Background</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extra 1</t>
+          <t xml:space="preserve">Background</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extra 1</t>
+          <t xml:space="preserve">Fondo</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_ExtraColor2</t>
+          <t xml:space="preserve">ThemeColors_Name_BackgroundLight</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extra 2</t>
+          <t xml:space="preserve">Background light</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extra 2</t>
+          <t xml:space="preserve">Fondo claro</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2329,17 +2329,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_ExtraColor3</t>
+          <t xml:space="preserve">ThemeColors_Name_CardBackground</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extra 3</t>
+          <t xml:space="preserve">Card</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extra 3</t>
+          <t xml:space="preserve">Tarjeta</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_ExtraColor4</t>
+          <t xml:space="preserve">ThemeColors_Name_CardBackgroundLight</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extra 4</t>
+          <t xml:space="preserve">Card light</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extra 4</t>
+          <t xml:space="preserve">Tarjeta clara</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_Success</t>
+          <t xml:space="preserve">ThemeColors_Name_Danger</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Success</t>
+          <t xml:space="preserve">Danger</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Éxito</t>
+          <t xml:space="preserve">Peligro</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2425,17 +2425,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_Text</t>
+          <t xml:space="preserve">ThemeColors_Name_ExtraColor1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text</t>
+          <t xml:space="preserve">Extra 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texto</t>
+          <t xml:space="preserve">Extra 1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2457,17 +2457,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_TextSecondary</t>
+          <t xml:space="preserve">ThemeColors_Name_ExtraColor2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary text</t>
+          <t xml:space="preserve">Extra 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texto secundario</t>
+          <t xml:space="preserve">Extra 2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Name_Warning</t>
+          <t xml:space="preserve">ThemeColors_Name_ExtraColor3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warning</t>
+          <t xml:space="preserve">Extra 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aviso</t>
+          <t xml:space="preserve">Extra 3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2521,17 +2521,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Revert</t>
+          <t xml:space="preserve">ThemeColors_Name_ExtraColor4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revert</t>
+          <t xml:space="preserve">Extra 4</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revertir</t>
+          <t xml:space="preserve">Extra 4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2553,17 +2553,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Swatches</t>
+          <t xml:space="preserve">ThemeColors_Name_Success</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Swatches (base + opacity)</t>
+          <t xml:space="preserve">Success</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muestras (base + opacidades)</t>
+          <t xml:space="preserve">Éxito</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">ThemeColors_Title</t>
+          <t xml:space="preserve">ThemeColors_Name_Text</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theme colours</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colores del tema</t>
+          <t xml:space="preserve">Texto</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2612,22 +2612,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lista de productos</t>
+          <t xml:space="preserve">Editor de colores del tema</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_Count_Format</t>
+          <t xml:space="preserve">ThemeColors_Name_TextSecondary</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Showing {0} of {1} products</t>
+          <t xml:space="preserve">Secondary text</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mostrando {0} de {1} productos</t>
+          <t xml:space="preserve">Texto secundario</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2644,22 +2644,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lista de productos</t>
+          <t xml:space="preserve">Editor de colores del tema</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_Filter_Placeholder</t>
+          <t xml:space="preserve">ThemeColors_Name_Warning</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filter by name…</t>
+          <t xml:space="preserve">Warning</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filtrar por nombre…</t>
+          <t xml:space="preserve">Aviso</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2676,22 +2676,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lista de productos</t>
+          <t xml:space="preserve">Editor de colores del tema</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_FilterAlert_Label</t>
+          <t xml:space="preserve">ThemeColors_Picker_Header</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">With price alert</t>
+          <t xml:space="preserve">COLOR PICKER</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Con alerta de precio</t>
+          <t xml:space="preserve">SELECTOR DE COLOR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2708,22 +2708,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lista de productos</t>
+          <t xml:space="preserve">Editor de colores del tema</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_FilterFavorites_Label</t>
+          <t xml:space="preserve">ThemeColors_Revert</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favourites</t>
+          <t xml:space="preserve">Revert</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Favoritos</t>
+          <t xml:space="preserve">Revertir</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2740,22 +2740,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lista de productos</t>
+          <t xml:space="preserve">Editor de colores del tema</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_FilterIssues_Label</t>
+          <t xml:space="preserve">ThemeColors_Swatches</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">With warnings</t>
+          <t xml:space="preserve">SWATCHES (BASE + OPACITY)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Con avisos</t>
+          <t xml:space="preserve">MUESTRAS (BASE + OPACIDADES)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2772,22 +2772,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lista de productos</t>
+          <t xml:space="preserve">Editor de colores del tema</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_FilterPriceChange_Label</t>
+          <t xml:space="preserve">ThemeColors_Title</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">With price change</t>
+          <t xml:space="preserve">Theme colours</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Con cambio de precio</t>
+          <t xml:space="preserve">Colores del tema</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2804,22 +2804,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lista de productos</t>
+          <t xml:space="preserve">Editor de colores del tema</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_FilterPurchased_Label</t>
+          <t xml:space="preserve">ThemeColors_UseContrastText_Label</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchased</t>
+          <t xml:space="preserve">Use contrast colour on background</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comprados</t>
+          <t xml:space="preserve">Usar color de contraste sobre el fondo</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_Filters_Tooltip</t>
+          <t xml:space="preserve">ProductList_Count_Format</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filters</t>
+          <t xml:space="preserve">Showing {0} of {1} products</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filtros</t>
+          <t xml:space="preserve">Mostrando {0} de {1} productos</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_Sort_Tooltip</t>
+          <t xml:space="preserve">ProductList_Filter_Placeholder</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sort</t>
+          <t xml:space="preserve">Filter by name…</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordenar</t>
+          <t xml:space="preserve">Filtrar por nombre…</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_SortPriceAsc_Label</t>
+          <t xml:space="preserve">ProductList_FilterAlert_Label</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Price: low to high</t>
+          <t xml:space="preserve">With price alert</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precio: de menor a mayor</t>
+          <t xml:space="preserve">Con alerta de precio</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2937,17 +2937,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductList_SortPriceDesc_Label</t>
+          <t xml:space="preserve">ProductList_FilterFavorites_Label</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Price: high to low</t>
+          <t xml:space="preserve">Favourites</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precio: de mayor a menor</t>
+          <t xml:space="preserve">Favoritos</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2964,22 +2964,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Log de la app</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">AppLog_Loaded_Progress</t>
+          <t xml:space="preserve">ProductList_FilterHistoricalLow_Label</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracker started</t>
+          <t xml:space="preserve">At historical low</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracker iniciado</t>
+          <t xml:space="preserve">En mínimo histórico</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2996,22 +2996,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_Email_Label</t>
+          <t xml:space="preserve">ProductList_FilterIssues_Label</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email or phone</t>
+          <t xml:space="preserve">With warnings</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email o teléfono</t>
+          <t xml:space="preserve">Con avisos</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3028,22 +3028,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_Email_Placeholder</t>
+          <t xml:space="preserve">ProductList_FilterPriceChange_Label</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">you@example.com</t>
+          <t xml:space="preserve">With price change</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">tucorreo@ejemplo.com</t>
+          <t xml:space="preserve">Con cambio de precio</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3060,22 +3060,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_Message</t>
+          <t xml:space="preserve">ProductList_FilterPurchased_Label</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter your Amazon credentials. They are used only to fill in the sign-in form and are not stored.</t>
+          <t xml:space="preserve">Purchased</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Introduce tus credenciales de Amazon. Solo se usan para rellenar el formulario de acceso; no se almacenan.</t>
+          <t xml:space="preserve">Comprados</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3092,22 +3092,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_NoBrowser_Message</t>
+          <t xml:space="preserve">ProductList_Filters_Tooltip</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add the web browser widget to a slot first, so the Amazon sign-in page can be shown.</t>
+          <t xml:space="preserve">Filters</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coloca antes el widget de navegador web en un hueco, para poder mostrar la página de acceso de Amazon.</t>
+          <t xml:space="preserve">Filtros</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3124,22 +3124,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_NoBrowser_Title</t>
+          <t xml:space="preserve">ProductList_FilterWithoutPrice_Label</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web browser not ready</t>
+          <t xml:space="preserve">Without price</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navegador web no disponible</t>
+          <t xml:space="preserve">Sin precio</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3156,22 +3156,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_Note</t>
+          <t xml:space="preserve">ProductList_PriceRange_Tooltip</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">If Amazon asks for a captcha or a verification code, complete it in the web browser widget. Your session is then kept between launches.</t>
+          <t xml:space="preserve">Filter by price range</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Si Amazon pide un captcha o un código de verificación, complétalo en el widget de navegador web. Después, la sesión se mantiene entre arranques.</t>
+          <t xml:space="preserve">Filtrar por rango de precio</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3188,22 +3188,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_Password_Label</t>
+          <t xml:space="preserve">ProductList_Sort_Tooltip</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Password</t>
+          <t xml:space="preserve">Sort</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contraseña</t>
+          <t xml:space="preserve">Ordenar</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3220,22 +3220,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_Progress_Done</t>
+          <t xml:space="preserve">ProductList_SortDateAsc_Label</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signed in to Amazon: {0}/{1} stores</t>
+          <t xml:space="preserve">Added: oldest first</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sesión de Amazon iniciada: {0}/{1} tiendas</t>
+          <t xml:space="preserve">Añadido: más antiguos primero</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3252,22 +3252,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_Progress_SigningIn</t>
+          <t xml:space="preserve">ProductList_SortDateDesc_Label</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signing in to {0} ({1}/{2})…</t>
+          <t xml:space="preserve">Added: newest first</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iniciando sesión en {0} ({1}/{2})…</t>
+          <t xml:space="preserve">Añadido: más recientes primero</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3284,22 +3284,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_SignIn_Label</t>
+          <t xml:space="preserve">ProductList_SortPriceAsc_Label</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign in</t>
+          <t xml:space="preserve">Price: low to high</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iniciar sesión</t>
+          <t xml:space="preserve">Precio: de menor a mayor</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3316,22 +3316,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Lista de productos</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_Title</t>
+          <t xml:space="preserve">ProductList_SortPriceDesc_Label</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign in to Amazon</t>
+          <t xml:space="preserve">Price: high to low</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iniciar sesión en Amazon</t>
+          <t xml:space="preserve">Precio: de mayor a menor</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3348,22 +3348,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login de Amazon</t>
+          <t xml:space="preserve">Log de la app</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogin_Tooltip</t>
+          <t xml:space="preserve">AppLog_Loaded_Progress</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign in to Amazon</t>
+          <t xml:space="preserve">Tracker started</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iniciar sesión en Amazon</t>
+          <t xml:space="preserve">Tracker iniciado</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3380,22 +3380,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logout de Amazon</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogout_Confirm_Label</t>
+          <t xml:space="preserve">AmazonLogin_Email_Label</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign out</t>
+          <t xml:space="preserve">Email or phone</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrar sesión</t>
+          <t xml:space="preserve">Email o teléfono</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3412,22 +3412,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logout de Amazon</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogout_ConfirmMessage</t>
+          <t xml:space="preserve">AmazonLogin_Email_Placeholder</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign out of your Amazon session in the browser?</t>
+          <t xml:space="preserve">you@example.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Cerrar tu sesión de Amazon en el navegador?</t>
+          <t xml:space="preserve">tucorreo@ejemplo.com</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3444,22 +3444,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logout de Amazon</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogout_ConfirmTitle</t>
+          <t xml:space="preserve">AmazonLogin_Message</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign out of Amazon</t>
+          <t xml:space="preserve">Enter your Amazon credentials. They are used only to fill in the sign-in form and are not stored.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrar sesión de Amazon</t>
+          <t xml:space="preserve">Introduce tus credenciales de Amazon. Solo se usan para rellenar el formulario de acceso; no se almacenan.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3476,22 +3476,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logout de Amazon</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogout_Progress_Done</t>
+          <t xml:space="preserve">AmazonLogin_NoBrowser_Message</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signed out of Amazon</t>
+          <t xml:space="preserve">Add the web browser widget to a slot first, so the Amazon sign-in page can be shown.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sesión de Amazon cerrada</t>
+          <t xml:space="preserve">Coloca antes el widget de navegador web en un hueco, para poder mostrar la página de acceso de Amazon.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3508,22 +3508,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logout de Amazon</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogout_Progress_SigningOut</t>
+          <t xml:space="preserve">AmazonLogin_NoBrowser_Title</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signing out of {0} ({1}/{2})…</t>
+          <t xml:space="preserve">Web browser not ready</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrando sesión en {0} ({1}/{2})…</t>
+          <t xml:space="preserve">Navegador web no disponible</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3540,22 +3540,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logout de Amazon</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonLogout_Tooltip</t>
+          <t xml:space="preserve">AmazonLogin_Note</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign out of Amazon</t>
+          <t xml:space="preserve">If Amazon asks for a captcha or a verification code, complete it in the web browser widget. Your session is then kept between launches.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrar sesión de Amazon</t>
+          <t xml:space="preserve">Si Amazon pide un captcha o un código de verificación, complétalo en el widget de navegador web. Después, la sesión se mantiene entre arranques.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3572,22 +3572,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notificaciones de Windows</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notify_AlertReached_Line</t>
+          <t xml:space="preserve">AmazonLogin_Password_Label</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Target reached: {0} {1}</t>
+          <t xml:space="preserve">Password</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precio objetivo: {0} {1}</t>
+          <t xml:space="preserve">Contraseña</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3604,22 +3604,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notificaciones de Windows</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notify_BackInStock_Line</t>
+          <t xml:space="preserve">AmazonLogin_Progress_Done</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back in stock: {0}</t>
+          <t xml:space="preserve">Signed in to Amazon: {0}/{1} stores</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">De nuevo disponible: {0}</t>
+          <t xml:space="preserve">Sesión de Amazon iniciada: {0}/{1} tiendas</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3636,22 +3636,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notificaciones de Windows</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notify_NewLow_Line</t>
+          <t xml:space="preserve">AmazonLogin_Progress_SigningIn</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">New low: {0} {1}</t>
+          <t xml:space="preserve">Signing in to {0} ({1}/{2})…</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuevo mínimo: {0} {1}</t>
+          <t xml:space="preserve">Iniciando sesión en {0} ({1}/{2})…</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3668,22 +3668,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notificaciones de Windows</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notify_Open_Label</t>
+          <t xml:space="preserve">AmazonLogin_SignIn_Label</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Sign in</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abrir</t>
+          <t xml:space="preserve">Iniciar sesión</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3700,22 +3700,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notificaciones de Windows</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notify_PreorderReleased_Line</t>
+          <t xml:space="preserve">AmazonLogin_Title</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Now on sale: {0}</t>
+          <t xml:space="preserve">Sign in to Amazon</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya a la venta: {0}</t>
+          <t xml:space="preserve">Iniciar sesión en Amazon</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3732,22 +3732,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notificaciones de Windows</t>
+          <t xml:space="preserve">Login de Amazon</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notify_Summary_Line</t>
+          <t xml:space="preserve">AmazonLogin_Tooltip</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0} updated · {1} drops · {2} with issues</t>
+          <t xml:space="preserve">Sign in to Amazon</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0} actualizados · {1} bajadas · {2} con avisos</t>
+          <t xml:space="preserve">Iniciar sesión en Amazon</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3764,22 +3764,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notificaciones de Windows</t>
+          <t xml:space="preserve">Logout de Amazon</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notify_Summary_Title</t>
+          <t xml:space="preserve">AmazonLogout_Confirm_Label</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracker: price update</t>
+          <t xml:space="preserve">Sign out</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracker: actualización de precios</t>
+          <t xml:space="preserve">Cerrar sesión</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3796,22 +3796,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantillas (slots)</t>
+          <t xml:space="preserve">Logout de Amazon</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">TemplateSlots_BuiltIn_Tooltip</t>
+          <t xml:space="preserve">AmazonLogout_ConfirmMessage</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Built-in template (read-only)</t>
+          <t xml:space="preserve">Sign out of your Amazon session in the browser?</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantilla de la app (solo lectura)</t>
+          <t xml:space="preserve">¿Cerrar tu sesión de Amazon en el navegador?</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3828,22 +3828,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Producto (tooltips / estados)</t>
+          <t xml:space="preserve">Logout de Amazon</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product_Issues_Tooltip</t>
+          <t xml:space="preserve">AmazonLogout_ConfirmTitle</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unavailable or no price in some store</t>
+          <t xml:space="preserve">Sign out of Amazon</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">No disponible o sin precio en alguna tienda</t>
+          <t xml:space="preserve">Cerrar sesión de Amazon</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3860,22 +3860,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Producto (tooltips / estados)</t>
+          <t xml:space="preserve">Logout de Amazon</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product_Preorder_Tooltip</t>
+          <t xml:space="preserve">AmazonLogout_Progress_Done</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-order (not released yet)</t>
+          <t xml:space="preserve">Signed out of Amazon</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reserva (aún no publicado)</t>
+          <t xml:space="preserve">Sesión de Amazon cerrada</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3892,22 +3892,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Logout de Amazon</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_Added_Progress</t>
+          <t xml:space="preserve">AmazonLogout_Progress_SigningOut</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">New product added: {0}</t>
+          <t xml:space="preserve">Signing out of {0} ({1}/{2})…</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuevo producto añadido: {0}</t>
+          <t xml:space="preserve">Cerrando sesión en {0} ({1}/{2})…</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3924,22 +3924,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Logout de Amazon</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_AddedAndRead_Progress</t>
+          <t xml:space="preserve">AmazonLogout_Tooltip</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">New product added: {0} ({1}/{2} prices read)</t>
+          <t xml:space="preserve">Sign out of Amazon</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuevo producto añadido: {0} ({1}/{2} precios leídos)</t>
+          <t xml:space="preserve">Cerrar sesión de Amazon</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3956,22 +3956,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Notificaciones de Windows</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_AltLinkAdded_Progress</t>
+          <t xml:space="preserve">Notify_AlertReached_Line</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alternative link added to: {0}</t>
+          <t xml:space="preserve">Target reached: {0} {1}</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link alternativo añadido a: {0}</t>
+          <t xml:space="preserve">Precio objetivo: {0} {1}</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3988,22 +3988,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Notificaciones de Windows</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_LinkDuplicate_Progress</t>
+          <t xml:space="preserve">Notify_BackInStock_Line</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">That link is already tracked for: {0}</t>
+          <t xml:space="preserve">Back in stock: {0}</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ese enlace ya está en seguimiento para: {0}</t>
+          <t xml:space="preserve">De nuevo disponible: {0}</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4020,22 +4020,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Notificaciones de Windows</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_LinkRemoved_Progress</t>
+          <t xml:space="preserve">Notify_NewLow_Line</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link "{0}" removed from: {1}</t>
+          <t xml:space="preserve">{0} - New low: {1}</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enlace "{0}" eliminado de: {1}</t>
+          <t xml:space="preserve">{0} - Nuevo mínimo: {1}</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4052,22 +4052,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Notificaciones de Windows</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_LinkRestored_Progress</t>
+          <t xml:space="preserve">Notify_Open_Label</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link "{0}" restored to: {1}</t>
+          <t xml:space="preserve">Open</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enlace "{0}" restaurado en: {1}</t>
+          <t xml:space="preserve">Abrir</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4084,22 +4084,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Notificaciones de Windows</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_Purchased_Progress</t>
+          <t xml:space="preserve">Notify_PreorderReleased_Line</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product marked as purchased: {0}</t>
+          <t xml:space="preserve">Now on sale: {0}</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Producto marcado como comprado: {0}</t>
+          <t xml:space="preserve">Ya a la venta: {0}</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4116,22 +4116,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Notificaciones de Windows</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_ReadingStore_Progress</t>
+          <t xml:space="preserve">Notify_Summary_Line</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reading {0} — {1}…</t>
+          <t xml:space="preserve">{0} updated · {1} drops · {2} with issues</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leyendo {0} — {1}…</t>
+          <t xml:space="preserve">{0} actualizados · {1} bajadas · {2} con avisos</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4148,22 +4148,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Notificaciones de Windows</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_Refreshed_Progress</t>
+          <t xml:space="preserve">Notify_Summary_Title</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}: {1}/{2} prices read</t>
+          <t xml:space="preserve">Tracker: price update</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0}: {1}/{2} precios leídos</t>
+          <t xml:space="preserve">Tracker: actualización de precios</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4180,22 +4180,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Plantillas (nombres)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_RefreshedAll_Progress</t>
+          <t xml:space="preserve">Template_Basic_Name</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prices updated: {0} product(s)</t>
+          <t xml:space="preserve">Basic layout</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precios actualizados: {0} producto(s)</t>
+          <t xml:space="preserve">Diseño básico</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4212,22 +4212,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Plantillas (nombres)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_Refreshing_Progress</t>
+          <t xml:space="preserve">Template_Full_Name</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reading prices for {0}…</t>
+          <t xml:space="preserve">Full layout</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leyendo precios de {0}…</t>
+          <t xml:space="preserve">Diseño completo</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4244,22 +4244,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Plantillas (nombres)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_RefreshingAll_Progress</t>
+          <t xml:space="preserve">Template_Normal_Name</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refreshing prices: {0} ({1}/{2})</t>
+          <t xml:space="preserve">Normal layout</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refrescando precios: {0} ({1}/{2})</t>
+          <t xml:space="preserve">Diseño normal</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4276,22 +4276,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Producto (tooltips / estados)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_Removed_Progress</t>
+          <t xml:space="preserve">Product_Issues_Tooltip</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product removed: {0}</t>
+          <t xml:space="preserve">Unavailable or no price in some store</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Producto borrado: {0}</t>
+          <t xml:space="preserve">No disponible o sin precio en alguna tienda</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4308,22 +4308,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registro de actividad (log)</t>
+          <t xml:space="preserve">Producto (tooltips / estados)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">ProductLog_Unpurchased_Progress</t>
+          <t xml:space="preserve">Product_Preorder_Tooltip</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0} marked as not purchased</t>
+          <t xml:space="preserve">Pre-order (not released yet)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0} marcado como no comprado</t>
+          <t xml:space="preserve">Reserva (aún no publicado)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4340,22 +4340,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selector de tipo de gráfica</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChartType_All_Label</t>
+          <t xml:space="preserve">ProductLog_Added_Progress</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">All</t>
+          <t xml:space="preserve">New product added: {0}</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Todos</t>
+          <t xml:space="preserve">Nuevo producto añadido: {0}</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4372,22 +4372,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selector de tipo de gráfica</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChartType_Area_Label</t>
+          <t xml:space="preserve">ProductLog_AddedAndRead_Progress</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Area</t>
+          <t xml:space="preserve">New product added: {0} ({1}/{2} prices read)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Área</t>
+          <t xml:space="preserve">Nuevo producto añadido: {0} ({1}/{2} precios leídos)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4404,22 +4404,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selector de tipo de gráfica</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChartType_Bars_Label</t>
+          <t xml:space="preserve">ProductLog_AltLinkAdded_Progress</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bars</t>
+          <t xml:space="preserve">Alternative link added to: {0}</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barras</t>
+          <t xml:space="preserve">Link alternativo añadido a: {0}</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4436,22 +4436,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selector de tipo de gráfica</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChartType_HBars_Label</t>
+          <t xml:space="preserve">ProductLog_AltStoresOff_Progress</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">H-Bars</t>
+          <t xml:space="preserve">Stopped tracking amazon.com and amazon.co.jp: {0}</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barras H</t>
+          <t xml:space="preserve">Ya no se siguen amazon.com y amazon.co.jp: {0}</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4468,22 +4468,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selector de tipo de gráfica</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChartType_Line_Label</t>
+          <t xml:space="preserve">ProductLog_AltStoresOn_Progress</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Line</t>
+          <t xml:space="preserve">Now tracking amazon.com and amazon.co.jp: {0}</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Línea</t>
+          <t xml:space="preserve">Ahora se siguen amazon.com y amazon.co.jp: {0}</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4500,22 +4500,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selector de tipo de gráfica</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChartType_Pie_Label</t>
+          <t xml:space="preserve">ProductLog_LinkDuplicate_Progress</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pie</t>
+          <t xml:space="preserve">That link is already tracked for: {0}</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circular</t>
+          <t xml:space="preserve">Ese enlace ya está en seguimiento para: {0}</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4532,22 +4532,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selector de tipo de gráfica</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChartType_Ring_Label</t>
+          <t xml:space="preserve">ProductLog_LinkRemoved_Progress</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ring</t>
+          <t xml:space="preserve">Link "{0}" removed from: {1}</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anillo</t>
+          <t xml:space="preserve">Enlace "{0}" eliminado de: {1}</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4564,22 +4564,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selector de tipo de gráfica</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChartType_SortAsc_Label</t>
+          <t xml:space="preserve">ProductLog_LinkRestored_Progress</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ascending</t>
+          <t xml:space="preserve">Link "{0}" restored to: {1}</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ascendente</t>
+          <t xml:space="preserve">Enlace "{0}" restaurado en: {1}</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4596,22 +4596,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selector de tipo de gráfica</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChartType_SortDesc_Label</t>
+          <t xml:space="preserve">ProductLog_Purchased_Progress</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descending</t>
+          <t xml:space="preserve">Product marked as purchased: {0}</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Descendente</t>
+          <t xml:space="preserve">Producto marcado como comprado: {0}</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4628,22 +4628,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selector de tipo de gráfica</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChartType_SortNone_Label</t>
+          <t xml:space="preserve">ProductLog_ReadingStore_Progress</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">No sort</t>
+          <t xml:space="preserve">Reading {0} — {1}…</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sin orden</t>
+          <t xml:space="preserve">Leyendo {0} — {1}…</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4660,22 +4660,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sesión de Amazon</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">AmazonSession_Startup_Log</t>
+          <t xml:space="preserve">ProductLog_Refreshed_Progress</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amazon: signed in to {0} of {1} stores</t>
+          <t xml:space="preserve">{0}: {1}/{2} prices read</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amazon: sesión iniciada en {0} de {1} tiendas</t>
+          <t xml:space="preserve">{0}: {1}/{2} precios leídos</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4692,22 +4692,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventana de ajustes (categorías)</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">SettingsDialog_About_Title</t>
+          <t xml:space="preserve">ProductLog_RefreshedAll_Progress</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">About</t>
+          <t xml:space="preserve">Prices updated: {0} product(s)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acerca de</t>
+          <t xml:space="preserve">Precios actualizados: {0} producto(s)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4724,22 +4724,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventana de ajustes (categorías)</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">SettingsDialog_General_Title</t>
+          <t xml:space="preserve">ProductLog_Refreshing_Progress</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">General</t>
+          <t xml:space="preserve">Reading prices for {0}…</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">General</t>
+          <t xml:space="preserve">Leyendo precios de {0}…</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4756,22 +4756,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventana de ajustes (categorías)</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">SettingsDialog_Theme_Title</t>
+          <t xml:space="preserve">ProductLog_RefreshingAll_Progress</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theme</t>
+          <t xml:space="preserve">Refreshing prices: {0} ({1}/{2})</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tema</t>
+          <t xml:space="preserve">Refrescando precios: {0} ({1}/{2})</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4788,22 +4788,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventana de ajustes (placeholder)</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">DialogsSettingsControl_Placeholder_Text</t>
+          <t xml:space="preserve">ProductLog_Removed_Progress</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Select a category.</t>
+          <t xml:space="preserve">Product removed: {0}</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selecciona una categoría.</t>
+          <t xml:space="preserve">Producto borrado: {0}</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4820,22 +4820,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventana principal</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">MainWindow_ActivityLogWidget_Title</t>
+          <t xml:space="preserve">ProductLog_Restored_Progress</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACTIVITY LOG</t>
+          <t xml:space="preserve">Product restored: {0}</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGISTRO DE ACTIVIDAD</t>
+          <t xml:space="preserve">Producto restaurado: {0}</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4852,22 +4852,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventana principal</t>
+          <t xml:space="preserve">Registro de actividad (log)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">MainWindow_FavoritesWidget_Title</t>
+          <t xml:space="preserve">ProductLog_Unpurchased_Progress</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAVOURITES</t>
+          <t xml:space="preserve">{0} marked as not purchased</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAVORITOS</t>
+          <t xml:space="preserve">{0} marcado como no comprado</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4884,22 +4884,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventana principal</t>
+          <t xml:space="preserve">Selector de tipo de gráfica</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">MainWindow_ProductsOverviewWidget_Title</t>
+          <t xml:space="preserve">ChartType_All_Label</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRICE OVERVIEW</t>
+          <t xml:space="preserve">All</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESUMEN DE PRECIOS</t>
+          <t xml:space="preserve">Todos</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4916,22 +4916,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventana principal</t>
+          <t xml:space="preserve">Selector de tipo de gráfica</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">MainWindow_WebSearchWidget_Title</t>
+          <t xml:space="preserve">ChartType_Area_Label</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">WEB SEARCH</t>
+          <t xml:space="preserve">Area</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">BÚSQUEDA WEB</t>
+          <t xml:space="preserve">Área</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4948,22 +4948,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de tipo de gráfica</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Alert_Tooltip</t>
+          <t xml:space="preserve">ChartType_Bars_Label</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set alert price</t>
+          <t xml:space="preserve">Bars</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definir precio de alerta</t>
+          <t xml:space="preserve">Barras</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4980,22 +4980,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de tipo de gráfica</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_AlertDialog_Message</t>
+          <t xml:space="preserve">ChartType_HBars_Label</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flag the product when its best price is at or below this value. Leave empty to remove the alert.</t>
+          <t xml:space="preserve">H-Bars</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marca el producto cuando su mejor precio esté en o por debajo de este valor. Déjalo vacío para quitar la alerta.</t>
+          <t xml:space="preserve">Barras H</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5012,22 +5012,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de tipo de gráfica</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_AlertDialog_Title</t>
+          <t xml:space="preserve">ChartType_Line_Label</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alert price</t>
+          <t xml:space="preserve">Line</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precio de alerta</t>
+          <t xml:space="preserve">Línea</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5044,22 +5044,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de tipo de gráfica</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_AlertPrice_Placeholder</t>
+          <t xml:space="preserve">ChartType_Pie_Label</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alert price</t>
+          <t xml:space="preserve">Pie</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precio de alerta</t>
+          <t xml:space="preserve">Circular</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5076,22 +5076,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de tipo de gráfica</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_BelowAlert_Tooltip</t>
+          <t xml:space="preserve">ChartType_Ring_Label</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Best price at or below the alert price</t>
+          <t xml:space="preserve">Ring</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejor precio en o por debajo del precio de alerta</t>
+          <t xml:space="preserve">Anillo</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5108,22 +5108,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de tipo de gráfica</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_CurrentPrice_Label</t>
+          <t xml:space="preserve">ChartType_SortAsc_Label</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current</t>
+          <t xml:space="preserve">Ascending</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Actual</t>
+          <t xml:space="preserve">Ascendente</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5140,22 +5140,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de tipo de gráfica</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Delete_Tooltip</t>
+          <t xml:space="preserve">ChartType_SortDesc_Label</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete product</t>
+          <t xml:space="preserve">Descending</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borrar producto</t>
+          <t xml:space="preserve">Descendente</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5172,22 +5172,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de tipo de gráfica</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_DeleteDialog_Message</t>
+          <t xml:space="preserve">ChartType_SortNone_Label</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete "{0}" and its price history? This can be undone via the log entry.</t>
+          <t xml:space="preserve">No sort</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Borrar "{0}" y su histórico de precios? Puedes deshacerlo desde el registro de actividad.</t>
+          <t xml:space="preserve">Sin orden</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5204,22 +5204,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de widgets</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_DeleteDialog_Title</t>
+          <t xml:space="preserve">WidgetSelector_Console_Tooltip</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delete product</t>
+          <t xml:space="preserve">Activity log</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borrar producto</t>
+          <t xml:space="preserve">Registro de actividad</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5236,22 +5236,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de widgets</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Edit_Tooltip</t>
+          <t xml:space="preserve">WidgetSelector_Default_Tooltip</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit product title</t>
+          <t xml:space="preserve">Empty widget</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editar el título del producto</t>
+          <t xml:space="preserve">Widget vacío</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5268,22 +5268,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de widgets</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_EditDialog_Message</t>
+          <t xml:space="preserve">WidgetSelector_Favorites_Tooltip</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product title:</t>
+          <t xml:space="preserve">Favourites</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Título del producto:</t>
+          <t xml:space="preserve">Favoritos</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5300,22 +5300,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de widgets</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_EditDialog_Title</t>
+          <t xml:space="preserve">WidgetSelector_ProductsOverview_Tooltip</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit title</t>
+          <t xml:space="preserve">Price overview</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editar título</t>
+          <t xml:space="preserve">Resumen de precios</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5332,22 +5332,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Selector de widgets</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_EditName_Placeholder</t>
+          <t xml:space="preserve">WidgetSelector_WebView_Tooltip</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product title</t>
+          <t xml:space="preserve">Web Search</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Título del producto</t>
+          <t xml:space="preserve">Búsqueda web</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5364,22 +5364,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Sesión de Amazon</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Favorite_Tooltip</t>
+          <t xml:space="preserve">AmazonSession_Startup_Log</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toggle favourite</t>
+          <t xml:space="preserve">Amazon: signed in to {0} of {1} stores</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcar/quitar favorito</t>
+          <t xml:space="preserve">Amazon: sesión iniciada en {0} de {1} tiendas</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5396,22 +5396,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Ventana de ajustes (categorías)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Issues_Label</t>
+          <t xml:space="preserve">SettingsDialog_About_Title</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue</t>
+          <t xml:space="preserve">About</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aviso</t>
+          <t xml:space="preserve">Acerca de</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5428,22 +5428,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Ventana de ajustes (categorías)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_LowestPrice_Label</t>
+          <t xml:space="preserve">SettingsDialog_General_Title</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lowest</t>
+          <t xml:space="preserve">General</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mínimo</t>
+          <t xml:space="preserve">General</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5460,22 +5460,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Ventana de ajustes (categorías)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_NoPrime_Label</t>
+          <t xml:space="preserve">SettingsDialog_Theme_Title</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Prime</t>
+          <t xml:space="preserve">Theme</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sin Prime</t>
+          <t xml:space="preserve">Tema</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5492,22 +5492,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Ventana de ajustes (placeholder)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Preorder_Label</t>
+          <t xml:space="preserve">DialogsSettingsControl_Placeholder_Text</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-order</t>
+          <t xml:space="preserve">Select a category.</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reserva</t>
+          <t xml:space="preserve">Selecciona una categoría.</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5524,22 +5524,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Ventana principal</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Prime_Label</t>
+          <t xml:space="preserve">MainWindow_ActivityLogWidget_Title</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prime</t>
+          <t xml:space="preserve">ACTIVITY LOG</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prime</t>
+          <t xml:space="preserve">REGISTRO DE ACTIVIDAD</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5556,22 +5556,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Ventana principal</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Promo_Label</t>
+          <t xml:space="preserve">MainWindow_FavoritesWidget_Title</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promo</t>
+          <t xml:space="preserve">FAVOURITES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promo</t>
+          <t xml:space="preserve">FAVORITOS</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5588,22 +5588,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Ventana principal</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Purchased_Confirm_Label</t>
+          <t xml:space="preserve">MainWindow_ProductsOverviewWidget_Title</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark as purchased</t>
+          <t xml:space="preserve">PRICE OVERVIEW</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcar como comprado</t>
+          <t xml:space="preserve">RESUMEN DE PRECIOS</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5620,22 +5620,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget de producto / favoritos</t>
+          <t xml:space="preserve">Ventana principal</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Purchased_Label</t>
+          <t xml:space="preserve">MainWindow_WebSearchWidget_Title</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchased</t>
+          <t xml:space="preserve">WEB SEARCH</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comprado</t>
+          <t xml:space="preserve">BÚSQUEDA WEB</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5657,17 +5657,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Purchased_Tooltip</t>
+          <t xml:space="preserve">PriceChart_Alert_Tooltip</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark as purchased</t>
+          <t xml:space="preserve">Set alert price</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcar como comprado</t>
+          <t xml:space="preserve">Definir precio de alerta</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5689,17 +5689,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_PurchasedDialog_Message</t>
+          <t xml:space="preserve">PriceChart_AlertDialog_Message</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enter the purchase price for "{0}". The product will be marked as purchased.</t>
+          <t xml:space="preserve">Flag the product when its best price is at or below this value. Leave empty to remove the alert.</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Introduce el precio de compra de "{0}". El producto se marcará como comprado.</t>
+          <t xml:space="preserve">Marca el producto cuando su mejor precio esté en o por debajo de este valor. Déjalo vacío para quitar la alerta.</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5721,17 +5721,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_PurchasedDialog_Title</t>
+          <t xml:space="preserve">PriceChart_AlertDialog_Title</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark as purchased</t>
+          <t xml:space="preserve">Alert price</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcar como comprado</t>
+          <t xml:space="preserve">Precio de alerta</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5753,17 +5753,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_PurchasePrice_Placeholder</t>
+          <t xml:space="preserve">PriceChart_AlertPrice_Placeholder</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchase price</t>
+          <t xml:space="preserve">Alert price</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precio de compra</t>
+          <t xml:space="preserve">Precio de alerta</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5785,17 +5785,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Refresh_Tooltip</t>
+          <t xml:space="preserve">PriceChart_AltStores_Tooltip</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refresh product prices</t>
+          <t xml:space="preserve">Track other amazon stores</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Refrescar los precios del producto</t>
+          <t xml:space="preserve">Seguir otras tiendas de amazon</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5817,17 +5817,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_RemoveLink_Tooltip</t>
+          <t xml:space="preserve">PriceChart_BelowAlert_Tooltip</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove link</t>
+          <t xml:space="preserve">Best price at or below the alert price</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eliminar enlace</t>
+          <t xml:space="preserve">Mejor precio en o por debajo del precio de alerta</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5849,17 +5849,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_RemoveLinkDialog_Message</t>
+          <t xml:space="preserve">PriceChart_CurrentPrice_Label</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove the "{0}" link from "{1}"? You can undo this from the activity log.</t>
+          <t xml:space="preserve">Current</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Eliminar el enlace "{0}" de "{1}"? Puedes deshacerlo desde el registro de actividad.</t>
+          <t xml:space="preserve">Actual</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5881,17 +5881,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_RemoveLinkDialog_Title</t>
+          <t xml:space="preserve">PriceChart_Delete_Tooltip</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove link</t>
+          <t xml:space="preserve">Delete product</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eliminar enlace</t>
+          <t xml:space="preserve">Borrar producto</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5913,17 +5913,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Search_Tooltip</t>
+          <t xml:space="preserve">PriceChart_DeleteDialog_Message</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search on the selected Amazon store</t>
+          <t xml:space="preserve">Delete "{0}" and its price history? You can undo this in the activity log.</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buscar en la tienda de Amazon seleccionada</t>
+          <t xml:space="preserve">¿Borrar "{0}" y su histórico de precios? Puedes deshacerlo en el registro de actividad.</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">PriceChart_Shipping_Tooltip</t>
+          <t xml:space="preserve">PriceChart_DeleteDialog_Title</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping costs</t>
+          <t xml:space="preserve">Delete product</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gastos de envío</t>
+          <t xml:space="preserve">Borrar producto</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5972,22 +5972,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget navegador</t>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">WebView_AddAltLink_Tooltip</t>
+          <t xml:space="preserve">PriceChart_DropFromPeak_Format</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add alternative link to selected product</t>
+          <t xml:space="preserve">-{0}%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Añadir enlace alternativo al producto seleccionado</t>
+          <t xml:space="preserve">-{0}%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6004,22 +6004,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget navegador</t>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">WebView_AddProduct_Tooltip</t>
+          <t xml:space="preserve">PriceChart_Edit_Tooltip</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add product</t>
+          <t xml:space="preserve">Edit product title</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Añadir producto</t>
+          <t xml:space="preserve">Editar el título del producto</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6036,22 +6036,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget navegador</t>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">WebView_Country_Tooltip</t>
+          <t xml:space="preserve">PriceChart_EditDialog_Message</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amazon marketplace</t>
+          <t xml:space="preserve">Product title:</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marketplace de Amazon</t>
+          <t xml:space="preserve">Título del producto:</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6068,22 +6068,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget navegador</t>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">WebView_Init_Error</t>
+          <t xml:space="preserve">PriceChart_EditDialog_Title</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">The web browser (WebView2) could not be initialized.</t>
+          <t xml:space="preserve">Edit title</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">No se pudo inicializar el navegador web (WebView2).</t>
+          <t xml:space="preserve">Editar título</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6100,22 +6100,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Widget navegador</t>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">WebView_PickImage_Tooltip</t>
+          <t xml:space="preserve">PriceChart_EditName_Placeholder</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pick product image</t>
+          <t xml:space="preserve">Product title</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seleccionar la imagen del producto</t>
+          <t xml:space="preserve">Título del producto</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6132,30 +6132,830 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Favorite_Tooltip</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mark as favourite</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcar como favorito</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Issues_Label</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Issue</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aviso</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_LowestPrice_Label</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lowest</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mínimo</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_NoPrime_Label</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No Prime</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin Prime</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Preorder_Label</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pre-order</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reserva</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Prime_Label</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prime</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prime</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Promo_Label</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Promo</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Promo</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Purchased_Confirm_Label</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mark as purchased</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcar como comprado</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Purchased_Label</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purchased</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comprado</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Purchased_Tooltip</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mark as purchased</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcar como comprado</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_PurchasedDialog_Message</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enter the purchase price for "{0}". The product will be marked as purchased.</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Introduce el precio de compra de "{0}". El producto se marcará como comprado.</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_PurchasedDialog_Title</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mark as purchased</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marcar como comprado</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_PurchasedPrice_Label</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purchased price</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Precio de compra</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_PurchasePrice_Placeholder</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purchase price</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Precio de compra</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Refresh_Tooltip</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refresh product prices</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refrescar los precios del producto</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_RemoveLink_Tooltip</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove link</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eliminar enlace</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_RemoveLinkDialog_Message</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove the "{0}" link from "{1}"? You can undo this in the activity log.</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Eliminar el enlace "{0}" de "{1}"? Puedes deshacerlo en el registro de actividad.</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_RemoveLinkDialog_Title</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove link</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eliminar enlace</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Search_Tooltip</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Search on the selected Amazon store</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buscar en la tienda de Amazon seleccionada</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget de producto / favoritos</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PriceChart_Shipping_Tooltip</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shipping costs</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gastos de envío</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
           <t xml:space="preserve">Widget navegador</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WebView_AddAltLink_Tooltip</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add alternative link</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Añadir enlace alternativo</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget navegador</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WebView_AddProduct_Tooltip</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add product</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Añadir producto</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget navegador</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WebView_Country_Tooltip</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon marketplace</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marketplace de Amazon</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget navegador</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WebView_Init_Error</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The web browser (WebView2) could not be initialized.</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No se pudo inicializar el navegador web (WebView2).</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget navegador</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WebView_PickImage_Tooltip</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pick product image</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seleccionar la imagen del producto</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Widget navegador</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
         <is>
           <t xml:space="preserve">WebView_PickPrice_Tooltip</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t xml:space="preserve">Pick product price</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t xml:space="preserve">Seleccionar el precio del producto</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
+      <c r="E216" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
